--- a/study_plan/2026_weekly_study_checklist.xlsx
+++ b/study_plan/2026_weekly_study_checklist.xlsx
@@ -11,6 +11,10 @@
     <sheet name="阶段规划" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="执行说明" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="资源清单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="WorldModel项目路线" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GitHub仓库观察" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="接下来8周专项" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="前8周细化" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每周学习清单'!$A$1:$O$39</definedName>
@@ -570,7 +574,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CS61B/MIT 6.006：数组、链表、复杂度分析</t>
+          <t>B站算法课：每周5节，推进基础概念、数组、复杂度</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -635,7 +639,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>CS61B/MIT 6.006：栈、队列、哈希表</t>
+          <t>B站算法课：每周5节，推进栈、队列、哈希表</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -700,7 +704,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>CS61B：树、递归；3Blue1Brown：向量、矩阵</t>
+          <t>B站算法课：每周5节，推进树、递归；3Blue1Brown：向量、矩阵</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>CS61B：堆、并查集；StatQuest：条件概率、期望、方差</t>
+          <t>B站算法课：每周5节，推进堆、并查集；StatQuest：概率基础</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -830,7 +834,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>MIT 6.006：图、BFS、DFS；微积分入门：导数、链式法则</t>
+          <t>B站算法课：每周5节，推进图、BFS、DFS；微积分入门</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -895,7 +899,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>MIT 6.006：最短路、拓扑；MIT 18.06：特征值、SVD 直觉</t>
+          <t>B站算法课：每周5节，推进最短路、拓扑；MIT 18.06：特征值、SVD 直觉</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -960,7 +964,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>算法主课：二分、贪心；统计补充：MLE、正则化</t>
+          <t>B站算法课：每周5节，推进二分、贪心；统计补充：MLE、正则化</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>算法主课复盘：回溯、DP 入门</t>
+          <t>B站算法课：每周5节，推进回溯、DP 入门</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1085,17 +1089,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>机器学习基础 1</t>
+          <t>算法主线继续 + ML 延后接入</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CS229/MIT 6.036：监督学习、线性回归、逻辑回归</t>
+          <t>B站算法课：每周5节；PyTorch 轻量入门开始接触</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>学习线性回归、逻辑回归、损失函数</t>
+          <t>算法继续推进，同时开始接触建模基础</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>监督学习框架</t>
+          <t>监督学习框架基础概念</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1150,17 +1154,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>机器学习基础 2</t>
+          <t>算法主线继续 + 轻量 ML 基础</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CS229/MIT 6.036：SVM、树模型、模型评估</t>
+          <t>B站算法课：每周5节；机器学习基础概念补充</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>学习 SVM、树模型、评估指标</t>
+          <t>学习评估指标、基础建模思路</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CS61B / MIT 6.006 + 3Blue1Brown 线代 + MIT 18.06 前半段 + StatQuest 概率基础</t>
+          <t>B站左神/马士兵算法数据结构全家桶（每周5节） + 3Blue1Brown 线代 + MIT 18.06 前半段 + StatQuest 概率基础</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3148,12 +3152,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>CS229 / MIT 6.036 + PyTorch 官方教程 + D2L + CS231n 前半部分</t>
+          <t>B站算法课继续每周5节 + PyTorch 官方教程 + D2L + CS231n 前半部分</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>进入机器学习、PyTorch 与视觉基础主线</t>
+          <t>算法主线继续推进，同时逐步接入 PyTorch 与视觉基础</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3399,82 +3403,94 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>推荐日均学习时长</t>
+          <t>当前算法主课</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5-7 小时</t>
+          <t>B站左神/马士兵算法数据结构全家桶；每周固定学5节</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>每日建议结构</t>
+          <t>推荐日均学习时长</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>算法 1.5-2h + 课程 2h + 项目 1.5-2h + 复盘 0.5h</t>
+          <t>5-7 小时</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>核心成果</t>
+          <t>每日建议结构</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2 个主项目 + 150 题左右算法题 + 一套可投递简历</t>
+          <t>算法 1.5-2h + 课程 2h + 项目 1.5-2h + 复盘 0.5h</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>主项目 1</t>
+          <t>核心成果</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>经典控制环境中的 dynamics model + MPC</t>
+          <t>2 个主项目 + 150 题左右算法题 + 一套可投递简历</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>主项目 2</t>
+          <t>主项目 1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>二维物理世界的小型 world model</t>
+          <t>经典控制环境中的 dynamics model + MPC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>加分项</t>
+          <t>主项目 2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>MuJoCo 简化 model-based RL / 1D PINN</t>
+          <t>二维物理世界的小型 world model</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>加分项</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MuJoCo 简化 model-based RL / 1D PINN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>使用方式</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>每周开始前看‘本周课程建议’和‘本周重点’；每周结束更新完成状态、完成度、备注</t>
         </is>
@@ -3491,7 +3507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3524,148 +3540,1122 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CS61B / Princeton Algorithms / MIT 6.006</t>
+          <t>B站左神/马士兵算法数据结构全家桶（每周5节）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>主线必学</t>
+          <t>当前唯一主课</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>机器学习</t>
+          <t>算法补充</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CS229 / MIT 6.036</t>
+          <t>MIT 6.006 / CS61B / Princeton Algorithms</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>主线必学</t>
+          <t>查漏补缺，不再作为主线</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>深度学习</t>
+          <t>机器学习</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CS231n / PyTorch 官方教程 / D2L</t>
+          <t>CS229 / 6.036（后置）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>主线必学</t>
+          <t>不再与当前算法主课并行硬推</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>数学</t>
+          <t>深度学习</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MIT 18.06 / 3Blue1Brown / StatQuest</t>
+          <t>CS231n / PyTorch 官方教程 / D2L</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>线代、概率、微积分补底</t>
+          <t>主线必学</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>强化学习</t>
+          <t>数学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>David Silver RL / Sutton &amp; Barto / Spinning Up</t>
+          <t>MIT 18.06 / 3Blue1Brown / StatQuest</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>主线必学</t>
+          <t>线代、概率、微积分补底</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>仿真与控制</t>
+          <t>强化学习</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MuJoCo Docs / MIT Underactuated Robotics</t>
+          <t>David Silver RL / Sutton &amp; Barto / Spinning Up</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>中后期</t>
+          <t>主线必学</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>世界模型</t>
+          <t>仿真与控制</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>World Models / PlaNet / Dreamer 系列</t>
+          <t>MuJoCo Docs / MIT Underactuated Robotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>中后期主线</t>
+          <t>中后期</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>前沿阅读</t>
+          <t>世界模型</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>JEPA 相关文章</t>
+          <t>World Models / PlaNet / Dreamer 系列</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>只做轻量理解</t>
+          <t>中后期主线</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>前沿阅读</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>JEPA 相关文章</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>只做轻量理解</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>加分项</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>PINN / JAX</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>有余力再做</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>项目代号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>难度</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>预计时间</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>核心任务</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>StateWorld-Sim</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>二维物理状态模拟器</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>低-中</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1-2 周</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>自己实现 2D 小世界、碰撞、重力、rollout</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>world model 地基，训练状态表示与规则建模</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>StateWorld-Predictor</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>下一状态预测器</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1-2 周</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>用模拟器数据做 s_t -&gt; s_t+1 预测与多步 rollout</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>第一个真正的 world model 味道项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>State2Frame-Renderer</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>状态到图像序列渲染器</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1 周</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>把状态序列渲染成帧序列，形成可控视频数据</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>从状态世界过渡到图像/视频世界</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FrameWorld-Baseline</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>图像未来帧预测基线</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>中-高</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2-3 周</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>输入前几帧预测下一帧或未来帧</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>正式进入视频型 world model</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mini-Latent-WorldModel</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>轻量 latent world model</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3-4 周</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>编码器 + latent transition + 解码器</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>最关键的主项目，连接现代 world model 思维</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Video-WorldModel-Playground</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>轻量视频世界模型实验场</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3-6 周</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>参考 Open-Sora 思想做最小视频预测/生成实验</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>后期升级项目，不建议立即做</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>仓库/方向</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>当前建议</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>你该重点看什么</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CompVis/stable-diffusion</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>重点读</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>latent diffusion / encoder-decoder / UNet / conditioning</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>热度高，适合理解 latent generation，不作为当前主项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>hpcaitech/Open-Sora</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>重点读</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>video generation / 3D-VAE / 时空建模 / diffusion transformer</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>视频世界模型视野核心仓库，先读后轻量实验</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>danijar/dreamerv3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>重点读</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>control-style world model / imagined trajectories / actor-critic</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>主线思想仓库，帮助你理解正统 world model</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MagicDrive（关键词跟踪）</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>后续补充</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>autonomous driving world model / 条件视频生成</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>先做关键词调研，不作为近期主项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Emu（关键词跟踪）</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>后续补充</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>多模态生成 / vision-language foundation model</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>先做观察对象，不作为当前主线</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>主线项目</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>主线任务</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>副线仓库阅读</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>阶段输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>第1-2周</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>StateWorld-Sim</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>搭建二维状态世界、碰撞与重力、生成 rollout</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>读 DreamerV3 README 与方法图</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1页笔记：world model 的核心模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>第3-4周</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>StateWorld-Predictor</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>做一步预测、多步 rollout、误差分析</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>读 Stable Diffusion README 与 latent diffusion 基本结构</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1页笔记：什么是 latent space generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>第5周</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>State2Frame-Renderer</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>把状态序列渲染成帧序列</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>读 Open-Sora README/报告概览</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>输出时空建模流程图</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>第6-7周</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FrameWorld-Baseline</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>做图像未来帧预测 baseline</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>继续 Open-Sora 配置结构 + Dreamer imagined rollout</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>输出图像 world model baseline 复盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>第8周</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mini-Latent-WorldModel 启动</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>开始做 encoder + latent transition 的最小版本</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>MagicDrive / Emu 关键词调研</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>记录驾驶 world model 与多模态生成的区别</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>B站课进度</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>本周核心主题</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hot100</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>代码随想录</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>项目推进</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>本周输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>当前进度后连续5节</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>数组、复杂度、二分基础、递归入门、简单排序思想</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>两数之和；合并两个有序链表；有效的括号；二叉树的中序遍历；买卖股票的最佳时机；最大子数组和</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>数组前半：二分查找、移除元素、有序数组的平方、长度最小的子数组</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>路径搜索可视化：建目录、画网格、定义起终点和障碍、跑通 BFS</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>最小可运行网格搜索脚本 + BFS 笔记</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>链表、栈、队列、哈希表、双指针</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>反转链表；环形链表；最长连续序列；三数之和；盛最多水的容器；无重复字符的最长子串</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>链表前半：移除链表元素、反转链表、两两交换节点、删除倒数第N个结点</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>路径搜索可视化：加入 DFS、随机障碍、地图编辑、对比 BFS/DFS</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>BFS/DFS 对比可视化 + README 初稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>树、堆、优先队列、递归深入、二叉树遍历</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>二叉树的层序遍历；验证二叉搜索树；对称二叉树；翻转二叉树；二叉树的最大深度；从前序与中序构造二叉树</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>二叉树前半：前中后序遍历、层序遍历、翻转二叉树、对称二叉树</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>路径搜索项目收尾：加入 Dijkstra；项目2启动：任务调度/拓扑排序系统，定义任务节点格式</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>路径搜索项目 v1 + 算法对比图</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>图基础、BFS、DFS、拓扑排序、并查集/连通性</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>岛屿数量；课程表；腐烂的橘子；克隆图；实现 Trie；单词搜索</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>图论前半：岛屿问题、所有可达路径、并查集入门、拓扑排序相关题</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>任务调度系统：输入依赖图、输出执行顺序、加入优先级、可视化依赖</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>调度系统最小版 + 拓扑排序笔记</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>最短路、贪心、图优化、堆在图中的应用、DP 引入</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>零钱兑换；爬楼梯；打家劫舍；最长递增子序列；组合总和；跳跃游戏</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>贪心前半：分发饼干、摆动序列、最大子数组和、跳跃游戏</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>任务调度系统收尾；项目3启动：二维物理规则模拟器，先定义状态和边界</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>调度系统 v1 + 物理模拟器状态设计文档</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DP 基础、状态定义、转移方程、记忆化/递推、经典DP 入门</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>不同路径；最小路径和；编辑距离；最长公共子序列；分割等和子集；单词拆分</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>DP 前半：斐波那契、爬楼梯、最小花费爬楼梯、不同路径</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>二维物理规则模拟器：小球移动、边界碰撞、时间步更新、多次 rollout 保存</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>可连续播放的小球运动模拟器 + rollout 笔记</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DP 进阶、背包、区间/序列DP、递归到DP的转换、综合题型</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>最长回文子串；最长有效括号；乘积最大子数组；完全平方数；目标和；单词拆分（复刷）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>DP 后半：01背包基础、分割等和子集、最后一块石头的重量II、目标和</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>二维物理规则模拟器：加入重力、多个物体、简化碰撞、导出状态序列</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>可导出数据的物理模拟器 v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>再连续5节</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>综合复盘、高频题型、复杂度复习、模板归纳、阶段总结</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>LRU 缓存；搜索二维矩阵II；接雨水；旋转图像；合并区间；每日温度</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>回顾前7周错题；图/树/DP 各补1-2题</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>项目3收尾；项目4启动：StateWorld-Predictor，确定输入输出并做一步预测 baseline</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>阶段1项目总复盘 + world model 项目准备</t>
         </is>
       </c>
     </row>

--- a/study_plan/2026_weekly_study_checklist.xlsx
+++ b/study_plan/2026_weekly_study_checklist.xlsx
@@ -15,6 +15,10 @@
     <sheet name="GitHub仓库观察" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="接下来8周专项" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="前8周细化" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Kaggle项目建议" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AI辅助编程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Prompt工程化资源" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="每日时间安排" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'每周学习清单'!$A$1:$O$39</definedName>
@@ -3032,6 +3036,504 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>建议频率</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>练什么</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 拆解</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>每周2次，每次20-30分钟</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>把任务拆成目标、输入输出、模块、边界条件</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>提高你用 AI 辅助开发的效率</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>代码审查</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>每周2次，每次20-30分钟</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>检查 AI 生成代码的复杂度、边界和正确性</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>防止被 AI 胡说带偏</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AI 工作流</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>每周1-2次</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>让 AI 帮你搭目录、写测试、补 README、重构</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>把 AI 当工程助手，而不是替代学习</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>资源</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>建议重点</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>为什么现在学</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Prompt结构化</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic Prompt Engineering / 官方文档与示例</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>任务拆解、上下文组织、约束表达</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>先学会把需求写清楚，再让 AI 写代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Prompt结构化</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Prompting Guide / 官方最佳实践</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>角色、目标、输入输出格式、few-shot</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>适合练 notebook 指令和数据分析任务描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>工程化表达</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>System Design Primer（GitHub）</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>模块拆分、接口意识、边界条件</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>不要求现在学大系统，先学清晰拆模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>工程化表达</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Refactoring Guru</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>重构意识、代码味道、命名与结构</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>适合配合 AI 生成代码后做二次整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Notebook写作</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle Learn: Intro to Machine Learning / Pandas / Data Visualization</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>标准 notebook 结构、图表、结论表达</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>最适合你当前场景的 notebook 入门材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Notebook写作</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle 高票 Notebook（tracking / trajectory 类）</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>背景、EDA、baseline、结果、结论</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>重点模仿结构，不是照抄模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>实验记录</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Weights &amp; Biases Reports / Blog</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>实验记录、结果对比、图表讲述</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>学习怎么把实验过程写得像项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>代码质量</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>pytest 官方文档</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>最小测试、回归测试、边界样例</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>帮助你把 AI 生成脚本变成可维护项目</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>时间段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>建议任务</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08:00-09:30</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>B站算法主课</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>当天最需要脑子的主线内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>09:30-10:20</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hot100 1题</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>建立面试题感</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10:20-11:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>错题复盘 / 代码随想录</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>巩固当天算法主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>13:30-14:30</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>代码随想录专题刷题</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>跟算法主课专题同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle 项目分析 / notebook 阅读</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>做反馈型项目主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>15:30-16:30</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Prompt 结构化训练 / 工程化表达 / AI辅助编程训练</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>优先练任务拆解、模块设计、Kaggle notebook 结构；论文与GitHub阅读放次选</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>20:30-21:15</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>低脑力任务</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>流程图、TODO、复盘；README 放到项目已有雏形后再做</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>21:15-22:30</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>个人电脑项目编码</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>优先主线项目，再做 Kaggle notebook</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4330,7 +4832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4339,7 +4841,8 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4375,6 +4878,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Kaggle并行</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>本周输出</t>
         </is>
       </c>
@@ -4405,10 +4913,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>路径搜索可视化：建目录、画网格、定义起终点和障碍、跑通 BFS</t>
+          <t>项目A 路径搜索可视化：建目录、画网格、定义起终点和障碍、跑通 BFS</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Kaggle 仅做浏览：收藏 3-5 个 tracking / trajectory / frame prediction notebook</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>最小可运行网格搜索脚本 + BFS 笔记</t>
         </is>
@@ -4440,10 +4953,15 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>路径搜索可视化：加入 DFS、随机障碍、地图编辑、对比 BFS/DFS</t>
+          <t>项目A 路径搜索可视化：加入 DFS、随机障碍、地图编辑、对比 BFS/DFS</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>选 1 个体育 tracking 或轨迹预测 notebook，记录输入/标签/baseline</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>BFS/DFS 对比可视化 + README 初稿</t>
         </is>
@@ -4475,10 +4993,15 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>路径搜索项目收尾：加入 Dijkstra；项目2启动：任务调度/拓扑排序系统，定义任务节点格式</t>
+          <t>项目A 收尾：加入 Dijkstra；项目B 启动：任务调度/拓扑排序系统，定义任务节点格式</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>选定第一个 Kaggle 方向，并写 1 页项目分析</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>路径搜索项目 v1 + 算法对比图</t>
         </is>
@@ -4510,10 +5033,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>任务调度系统：输入依赖图、输出执行顺序、加入优先级、可视化依赖</t>
+          <t>项目B 任务调度系统：输入依赖图、输出执行顺序、加入优先级、可视化依赖</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>正式开始 Kaggle：拆 1 个 notebook 的结构，记录特征/baseline/指标</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>调度系统最小版 + 拓扑排序笔记</t>
         </is>
@@ -4545,10 +5073,15 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>任务调度系统收尾；项目3启动：二维物理规则模拟器，先定义状态和边界</t>
+          <t>项目B 收尾；项目C 启动：二维物理规则模拟器，先定义状态和边界</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>开始第一个 Kaggle baseline notebook：数据读取 + 可视化 + 最简单 baseline</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>调度系统 v1 + 物理模拟器状态设计文档</t>
         </is>
@@ -4580,10 +5113,15 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>二维物理规则模拟器：小球移动、边界碰撞、时间步更新、多次 rollout 保存</t>
+          <t>项目C 二维物理规则模拟器：小球移动、边界碰撞、时间步更新、多次 rollout 保存</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>完成 Kaggle baseline 第一版，并产出 2-3 张图</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>可连续播放的小球运动模拟器 + rollout 笔记</t>
         </is>
@@ -4615,10 +5153,15 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>二维物理规则模拟器：加入重力、多个物体、简化碰撞、导出状态序列</t>
+          <t>项目C 二维物理规则模拟器：加入重力、多个物体、简化碰撞、导出状态序列</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>改进 Kaggle baseline，并把 notebook 写成：背景/数据/baseline/结果</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>可导出数据的物理模拟器 v1</t>
         </is>
@@ -4650,12 +5193,199 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>项目3收尾；项目4启动：StateWorld-Predictor，确定输入输出并做一步预测 baseline</t>
+          <t>项目C 收尾；项目D 启动：StateWorld-Predictor，确定输入输出并做一步预测 baseline</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>完成第一个 Kaggle 项目第一版 notebook，形成公开展示结构</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>阶段1项目总复盘 + world model 项目准备</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>项目类型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>适合度</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>宽松时间</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>你会练到什么</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>当前建议</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>体育追踪/行为预测</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2-3 周</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>tracking data、时空行为、可视化反馈强</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>适合作为第一个 Kaggle 主项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>轨迹预测/自动驾驶类</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>3-4 周</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>trajectory forecasting、多主体状态预测</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>和 world model / 驾驶场景最接近</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>视频/帧序列预测</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>中-高</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3-5 周</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>future frame prediction、sequence modeling</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>适合作为视频型 world model 过渡项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>纯 tabular 排行赛</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1-2 周</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>反馈快，但和 world model 相关性弱</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>只建议作为补充</t>
         </is>
       </c>
     </row>
